--- a/Result/profitability/1104.xlsx
+++ b/Result/profitability/1104.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5687500000000001</v>
+        <v>0.57125</v>
       </c>
       <c r="N2" t="n">
-        <v>21.28375</v>
+        <v>22.27</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>0.49375</v>
+        <v>0.51375</v>
       </c>
       <c r="N3" t="n">
-        <v>19.85</v>
+        <v>20.53375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4025</v>
+        <v>0.43875</v>
       </c>
       <c r="N4" t="n">
-        <v>17.41125</v>
+        <v>18.16875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.13</v>
       </c>
       <c r="M5" t="n">
-        <v>0.33375</v>
+        <v>0.35125</v>
       </c>
       <c r="N5" t="n">
-        <v>15.03875</v>
+        <v>15.56125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>0.25125</v>
+        <v>0.2375</v>
       </c>
       <c r="N6" t="n">
-        <v>12.47375</v>
+        <v>13.195</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.54</v>
       </c>
       <c r="M7" t="n">
-        <v>0.21625</v>
+        <v>0.21</v>
       </c>
       <c r="N7" t="n">
-        <v>11.20125</v>
+        <v>10.8575</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>0.11125</v>
+        <v>0.14875</v>
       </c>
       <c r="N8" t="n">
-        <v>8.275</v>
+        <v>8.077500000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.15625</v>
       </c>
       <c r="N9" t="n">
-        <v>5.983750000000001</v>
+        <v>5.98375</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>-0.18</v>
       </c>
       <c r="M10" t="n">
-        <v>0.09250000000000003</v>
+        <v>0.0925</v>
       </c>
       <c r="N10" t="n">
         <v>5.06625</v>
@@ -1902,7 +1902,7 @@
         <v>0.33125</v>
       </c>
       <c r="N12" t="n">
-        <v>7.383750000000001</v>
+        <v>7.38375</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1325</v>
+      </c>
+      <c r="E75" t="n">
+        <v>475</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="G75" t="n">
+        <v>261</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.50%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>282</v>
+      </c>
+      <c r="J75" t="n">
+        <v>544</v>
+      </c>
+      <c r="K75" t="n">
+        <v>489</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6162500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7317073170731707</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.579999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05652951699463327</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2456140350877194</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1883731410545291</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
